--- a/3_Training_Validation/evaluation/feature_importances_ranked.xlsx
+++ b/3_Training_Validation/evaluation/feature_importances_ranked.xlsx
@@ -9,7 +9,20 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,13 +38,13 @@
     <t>Diff_PSSM_Score</t>
   </si>
   <si>
-    <t>e</t>
+    <t>FT5</t>
   </si>
   <si>
     <t>diff_foldx_total energy</t>
   </si>
   <si>
-    <t>c</t>
+    <t>FT3</t>
   </si>
   <si>
     <t>Diff_PSSM_Score_Aver</t>
@@ -40,7 +53,7 @@
     <t>wt_num_pharm_c_aromatics</t>
   </si>
   <si>
-    <t>b</t>
+    <t>FT2</t>
   </si>
   <si>
     <t>diff_aaindex1_Information measure for pleated-sheet (Robson-Suzuki, 1976)</t>
@@ -229,7 +242,7 @@
     <t>Temperature</t>
   </si>
   <si>
-    <t>a</t>
+    <t>FT1</t>
   </si>
   <si>
     <t>wt_pct_aa_c_nonpolar</t>
@@ -244,14 +257,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,13 +275,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -736,148 +742,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1596,7 +1602,7 @@
         <v>0.0110567267984152</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3">
